--- a/education_forms/014_digital_learning_platform_usability_evaluation_form--education_forms.xlsx
+++ b/education_forms/014_digital_learning_platform_usability_evaluation_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'online_learning_environment'}</t>
+          <t>online_learning_environment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Online Learning Environment'}</t>
+          <t>Online Learning Environment</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'online_course_site'}</t>
+          <t>online_course_site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Online Course Site'}</t>
+          <t>Online Course Site</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'lms'}</t>
+          <t>lms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'LMS'}</t>
+          <t>LMS</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'easy_to_use'}</t>
+          <t>easy_to_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Easy to use'}</t>
+          <t>Easy to use</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'confusing'}</t>
+          <t>confusing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Confusing'}</t>
+          <t>Confusing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'not_intuitive'}</t>
+          <t>not_intuitive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Not Intuitive'}</t>
+          <t>Not Intuitive</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'intuitive'}</t>
+          <t>intuitive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Intuitive'}</t>
+          <t>Intuitive</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'unintuitive'}</t>
+          <t>unintuitive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Unintuitive'}</t>
+          <t>Unintuitive</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'frustrating'}</t>
+          <t>frustrating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Frustrating'}</t>
+          <t>Frustrating</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'engaging'}</t>
+          <t>engaging</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Engaging'}</t>
+          <t>Engaging</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'disengaging'}</t>
+          <t>disengaging</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Disengaging'}</t>
+          <t>Disengaging</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_engaging'}</t>
+          <t>somewhat_engaging</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Engaging'}</t>
+          <t>Somewhat Engaging</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_disengaging'}</t>
+          <t>somewhat_disengaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Disengaging'}</t>
+          <t>Somewhat Disengaging</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_engaging'}</t>
+          <t>not_engaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not Engaging'}</t>
+          <t>Not Engaging</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'not_disengaging'}</t>
+          <t>not_disengaging</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Not Disengaging'}</t>
+          <t>Not Disengaging</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'ineffective'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Ineffective'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_ineffective'}</t>
+          <t>somewhat_ineffective</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Ineffective'}</t>
+          <t>Somewhat Ineffective</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'not_ineffective'}</t>
+          <t>not_ineffective</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Not Ineffective'}</t>
+          <t>Not Ineffective</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'unsatisfied'}</t>
+          <t>unsatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Unsatisfied'}</t>
+          <t>Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'not_unsatisfied'}</t>
+          <t>not_unsatisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Not Unsatisfied'}</t>
+          <t>Not Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Helpful'}</t>
+          <t>Helpful</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Not Helpful'}</t>
+          <t>Not Helpful</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Helpful'}</t>
+          <t>Somewhat Helpful</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_not_helpful'}</t>
+          <t>somewhat_not_helpful</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Not Helpful'}</t>
+          <t>Somewhat Not Helpful</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>platform_features_choices</t>
+          <t>platform_navigation_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'not_helpful'}</t>
+          <t>easy_to_navigate</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Not Helpful'}</t>
+          <t>Easy to navigate</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'easy_to_navigate'}</t>
+          <t>difficult_to_navigate</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Easy to navigate'}</t>
+          <t>Difficult to navigate</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'difficult_to_navigate'}</t>
+          <t>somewhat_easy_to_navigate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Difficult to navigate'}</t>
+          <t>Somewhat Easy to navigate</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_easy_to_navigate'}</t>
+          <t>somewhat_difficult_to_navigate</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Easy to navigate'}</t>
+          <t>Somewhat Difficult to navigate</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_difficult_to_navigate'}</t>
+          <t>not_easy_to_navigate</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Difficult to navigate'}</t>
+          <t>Not Easy to navigate</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'not_easy_to_navigate'}</t>
+          <t>not_difficult_to_navigate</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Not Easy to navigate'}</t>
+          <t>Not Difficult to navigate</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>platform_navigation_choices</t>
+          <t>platform_search_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'not_difficult_to_navigate'}</t>
+          <t>easy_to_search</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Not Difficult to navigate'}</t>
+          <t>Easy to search</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'easy_to_search'}</t>
+          <t>difficult_to_search</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Easy to search'}</t>
+          <t>Difficult to search</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'difficult_to_search'}</t>
+          <t>somewhat_easy_to_search</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Difficult to search'}</t>
+          <t>Somewhat Easy to search</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_easy_to_search'}</t>
+          <t>somewhat_difficult_to_search</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Easy to search'}</t>
+          <t>Somewhat Difficult to search</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_difficult_to_search'}</t>
+          <t>not_easy_to_search</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Difficult to search'}</t>
+          <t>Not Easy to search</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'not_easy_to_search'}</t>
+          <t>not_difficult_to_search</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Not Easy to search'}</t>
+          <t>Not Difficult to search</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>platform_search_choices</t>
+          <t>feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'not_difficult_to_search'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Not Difficult to search'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>feedback_improved_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>feedback_improved_choices</t>
+          <t>user_experience_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>engaging</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>Engaging</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'engaging'}</t>
+          <t>disengaging</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Engaging'}</t>
+          <t>Disengaging</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'disengaging'}</t>
+          <t>somewhat_engaging</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Disengaging'}</t>
+          <t>Somewhat Engaging</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_engaging'}</t>
+          <t>somewhat_disengaging</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Engaging'}</t>
+          <t>Somewhat Disengaging</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_disengaging'}</t>
+          <t>not_engaging</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Disengaging'}</t>
+          <t>Not Engaging</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'not_engaging'}</t>
+          <t>not_disengaging</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Not Engaging'}</t>
+          <t>Not Disengaging</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>user_experience_choices</t>
+          <t>platform_usability_improved_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'not_disengaging'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Not Disengaging'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2117,29 +2117,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>platform_usability_improved_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>engaging</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>Engaging</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'engaging'}</t>
+          <t>disengaging</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Engaging'}</t>
+          <t>Disengaging</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'disengaging'}</t>
+          <t>somewhat_engaging</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Disengaging'}</t>
+          <t>Somewhat Engaging</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_engaging'}</t>
+          <t>somewhat_disengaging</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Engaging'}</t>
+          <t>Somewhat Disengaging</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_disengaging'}</t>
+          <t>not_engaging</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Disengaging'}</t>
+          <t>Not Engaging</t>
         </is>
       </c>
     </row>
@@ -2219,29 +2219,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'not_engaging'}</t>
+          <t>not_disengaging</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Not Engaging'}</t>
+          <t>Not Disengaging</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>overall_experience_choices</t>
+          <t>platform_effectiveness_improved_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'not_disengaging'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Not Disengaging'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2270,29 +2270,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>platform_effectiveness_improved_choices</t>
+          <t>user_satisfaction_improved_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2321,29 +2321,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>user_satisfaction_improved_choices</t>
+          <t>platform_features_improved_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2372,29 +2372,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>platform_features_improved_choices</t>
+          <t>overall_experience_improved_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2423,29 +2423,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>overall_experience_improved_choices</t>
+          <t>platform_navigation_improved_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2474,29 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>platform_navigation_improved_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>{'value':_'unsure'}</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
